--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484241_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484241_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.566599999999999</v>
+        <v>7.2868</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3021</v>
+        <v>6.5943</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2645</v>
+        <v>0.6925</v>
       </c>
       <c r="G2" t="n">
         <v>4.1024</v>
@@ -610,13 +610,13 @@
         <v>2.5395</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6753</v>
+        <v>1.3956</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3236</v>
+        <v>0.6158</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3517</v>
+        <v>0.7798</v>
       </c>
       <c r="V2" t="n">
         <v>3.1563</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.5916</v>
+        <v>6.8178</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6403</v>
+        <v>5.7302</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9514</v>
+        <v>1.0875</v>
       </c>
       <c r="G3" t="n">
         <v>2.6116</v>
@@ -688,13 +688,13 @@
         <v>0.3907</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7554</v>
+        <v>0.9815</v>
       </c>
       <c r="T3" t="n">
-        <v>1.175</v>
+        <v>0.2649</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5804</v>
+        <v>0.7166</v>
       </c>
       <c r="V3" t="n">
         <v>3.8107</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4875</v>
+        <v>0.5199</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.7659</v>
+        <v>-2.0581</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2784</v>
+        <v>2.578</v>
       </c>
       <c r="G4" t="n">
         <v>0.3965</v>
@@ -766,13 +766,13 @@
         <v>2.9301</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0286</v>
+        <v>0.9788</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4483</v>
+        <v>0.2595</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4197</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0.1213</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1036</v>
+        <v>-0.9324</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6066</v>
+        <v>1.5055</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.7103</v>
+        <v>-2.4379</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2427</v>
@@ -844,13 +844,13 @@
         <v>2.1488</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1624</v>
+        <v>0.3336</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3247</v>
+        <v>0.2236</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1624</v>
+        <v>0.11</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2186</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2642</v>
+        <v>-1.0269</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6524</v>
+        <v>-0.5512</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6119</v>
+        <v>-0.4757</v>
       </c>
       <c r="G6" t="n">
         <v>-1.6851</v>
@@ -922,13 +922,13 @@
         <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1651</v>
+        <v>0.0722</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.121</v>
+        <v>-0.0199</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.044</v>
+        <v>0.0921</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5723</v>
+        <v>-1.6114</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8197</v>
+        <v>-2.3141</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2474</v>
+        <v>0.7027</v>
       </c>
       <c r="G7" t="n">
         <v>-2.0879</v>
@@ -1000,13 +1000,13 @@
         <v>2.1488</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7497</v>
+        <v>1.7106</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0359</v>
+        <v>0.5415</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7138</v>
+        <v>1.1691</v>
       </c>
       <c r="V7" t="n">
         <v>-1.4294</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8755</v>
+        <v>-1.8483</v>
       </c>
       <c r="E8" t="n">
         <v>-1.0164</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8592</v>
+        <v>-0.832</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0769</v>
@@ -1078,13 +1078,13 @@
         <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2377</v>
+        <v>-0.2105</v>
       </c>
       <c r="T8" t="n">
         <v>-0.121</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1167</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3656</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1229</v>
+        <v>-1.8856</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2461</v>
+        <v>-1.145</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8768</v>
+        <v>-0.7407</v>
       </c>
       <c r="G9" t="n">
         <v>2.0699</v>
@@ -1156,13 +1156,13 @@
         <v>0.1953</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2394</v>
+        <v>-0.0021</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0138</v>
+        <v>0.1149</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2532</v>
+        <v>-0.117</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2186</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7541</v>
+        <v>-2.1784</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1458</v>
+        <v>-0.8425</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6083</v>
+        <v>-1.3359</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7443</v>
@@ -1234,13 +1234,13 @@
         <v>0.1953</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7208</v>
+        <v>-0.1452</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4842</v>
+        <v>-0.1808</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2367</v>
+        <v>0.0357</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4843</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0406</v>
+        <v>-3.2973</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.985</v>
+        <v>-3.1872</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0556</v>
+        <v>-0.1101</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1059</v>
@@ -1312,13 +1312,13 @@
         <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1825</v>
+        <v>0.9258</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6357</v>
+        <v>0.4335</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5468</v>
+        <v>0.4923</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7731</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5761</v>
+        <v>-4.4828</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.9763</v>
+        <v>-4.7741</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4003</v>
+        <v>0.2913</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9349</v>
@@ -1390,13 +1390,13 @@
         <v>2.1488</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9371</v>
+        <v>1.0303</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1432</v>
+        <v>0.3454</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.6849</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8201000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.638600000000001</v>
+        <v>-2.638599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.058600000000001</v>
+        <v>-2.058599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5801000000000001</v>
+        <v>-0.5803000000000003</v>
       </c>
       <c r="G13" t="n">
         <v>0.3027000000000015</v>
@@ -1468,13 +1468,13 @@
         <v>14.6507</v>
       </c>
       <c r="S13" t="n">
-        <v>7.0708</v>
+        <v>7.070599999999999</v>
       </c>
       <c r="T13" t="n">
         <v>2.4774</v>
       </c>
       <c r="U13" t="n">
-        <v>4.5933</v>
+        <v>4.5934</v>
       </c>
       <c r="V13" t="n">
         <v>-1.221399999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.7439</v>
+        <v>8.4932</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7815</v>
+        <v>6.2871</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9623</v>
+        <v>2.2061</v>
       </c>
       <c r="G14" t="n">
         <v>0.8943</v>
@@ -1546,13 +1546,13 @@
         <v>3.5162</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.9551</v>
+        <v>-1.2058</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4525</v>
+        <v>-0.947</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5026</v>
+        <v>-0.2588</v>
       </c>
       <c r="V14" t="n">
         <v>5.4838</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8001</v>
+        <v>1.4137</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3543</v>
+        <v>3.051</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5542</v>
+        <v>-1.6373</v>
       </c>
       <c r="G15" t="n">
         <v>1.3354</v>
@@ -1624,13 +1624,13 @@
         <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5894</v>
+        <v>0.203</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5009</v>
+        <v>0.1975</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0885</v>
+        <v>0.0054</v>
       </c>
       <c r="V15" t="n">
         <v>-1.8828</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5393</v>
+        <v>0.857</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4248</v>
+        <v>1.5259</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8854</v>
+        <v>-0.6689000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>-0.09710000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1732</v>
+        <v>-0.0721</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7215</v>
+        <v>-0.5049</v>
       </c>
       <c r="V16" t="n">
         <v>0.5545</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.183</v>
+        <v>0.7366</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7919</v>
+        <v>-1.5896</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9749</v>
+        <v>2.3262</v>
       </c>
       <c r="G17" t="n">
         <v>-1.5202</v>
@@ -1780,13 +1780,13 @@
         <v>3.9069</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9414</v>
+        <v>-0.3879</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6574</v>
+        <v>-0.4552</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.284</v>
+        <v>0.0673</v>
       </c>
       <c r="V17" t="n">
         <v>0.8865</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.08649999999999999</v>
+        <v>0.3244</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7242</v>
+        <v>-0.4208</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6377</v>
+        <v>0.7453</v>
       </c>
       <c r="G18" t="n">
         <v>0.3829</v>
@@ -1858,13 +1858,13 @@
         <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6647</v>
+        <v>-0.2538</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5447</v>
+        <v>-0.2414</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.12</v>
+        <v>-0.0124</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1857</v>
+        <v>-0.5255</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1395</v>
+        <v>-2.3417</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9537</v>
+        <v>1.8162</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7675</v>
@@ -1936,13 +1936,13 @@
         <v>3.3208</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8089</v>
+        <v>-1.1487</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.96</v>
+        <v>-1.1622</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1511</v>
+        <v>0.0136</v>
       </c>
       <c r="V19" t="n">
         <v>1.2186</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7845</v>
+        <v>-0.5679</v>
       </c>
       <c r="E20" t="n">
         <v>-0.4294</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3551</v>
+        <v>-0.1385</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1257</v>
@@ -2014,13 +2014,13 @@
         <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1314</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="T20" t="n">
         <v>-0.5447</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5867</v>
+        <v>-0.3701</v>
       </c>
       <c r="V20" t="n">
         <v>0.8865</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9114</v>
+        <v>-0.6754</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2571</v>
+        <v>-0.156</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6542</v>
+        <v>-0.5194</v>
       </c>
       <c r="G21" t="n">
         <v>1.5655</v>
@@ -2092,13 +2092,13 @@
         <v>2.9301</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3949</v>
+        <v>-1.159</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0894</v>
+        <v>-0.9883</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3055</v>
+        <v>-0.1707</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8865</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9504</v>
+        <v>-0.8298</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1536</v>
+        <v>-0.9514</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2032</v>
+        <v>0.1215</v>
       </c>
       <c r="G22" t="n">
         <v>1.811</v>
@@ -2170,13 +2170,13 @@
         <v>2.3441</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5195</v>
+        <v>-0.3989</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9684</v>
+        <v>-0.7661</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4489</v>
+        <v>0.3672</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4373</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.234</v>
+        <v>-2.0286</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1439</v>
+        <v>-1.155</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0901</v>
+        <v>-0.8736</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8474</v>
@@ -2248,13 +2248,13 @@
         <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>1.3092</v>
+        <v>0.5145</v>
       </c>
       <c r="T23" t="n">
-        <v>1.6592</v>
+        <v>0.648</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.35</v>
+        <v>-0.1335</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1097</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4752</v>
+        <v>-3.2107</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.341</v>
+        <v>-3.2399</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1342</v>
+        <v>0.0292</v>
       </c>
       <c r="G24" t="n">
         <v>0.0663</v>
@@ -2326,13 +2326,13 @@
         <v>0.586</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6587</v>
+        <v>-0.3941</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3631</v>
+        <v>-0.262</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2955</v>
+        <v>-0.1321</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4921</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.638600000000001</v>
+        <v>3.987</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5799999999999987</v>
+        <v>0.5802000000000009</v>
       </c>
       <c r="F25" t="n">
-        <v>2.0586</v>
+        <v>3.4068</v>
       </c>
       <c r="G25" t="n">
         <v>-0.3025000000000002</v>
@@ -2404,13 +2404,13 @@
         <v>23.4411</v>
       </c>
       <c r="S25" t="n">
-        <v>-7.0707</v>
+        <v>-5.722600000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.593299999999999</v>
+        <v>-4.593500000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.4773</v>
+        <v>-1.129</v>
       </c>
       <c r="V25" t="n">
         <v>1.2215</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484241_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484241_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-2.3276</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>0.2096</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>A. BENNASSAR ROSSELLÓ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5199</v>
+        <v>0.607</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.0581</v>
+        <v>0.607</v>
       </c>
       <c r="F4" t="n">
-        <v>2.578</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3965</v>
+        <v>0.607</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2988</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9023</v>
+        <v>0.607</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5892</v>
+        <v>0.607</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3561</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7669</v>
+        <v>0.607</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1927</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0573</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1354</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9301</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9788</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2595</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7193000000000001</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1213</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1213</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>E. ZUSTOVICH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9324</v>
+        <v>0.5199</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5055</v>
+        <v>-2.0581</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.4379</v>
+        <v>2.578</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2427</v>
+        <v>0.3965</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4454</v>
+        <v>1.2988</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6881</v>
+        <v>-0.9023</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7395</v>
+        <v>1.5892</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6181</v>
+        <v>2.3561</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1214</v>
+        <v>-0.7669</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9822</v>
+        <v>-1.1927</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1727</v>
+        <v>-1.0573</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8095</v>
+        <v>-0.1354</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1488</v>
+        <v>2.9301</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3336</v>
+        <v>0.9788</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2236</v>
+        <v>0.2595</v>
       </c>
       <c r="U5" t="n">
-        <v>0.11</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2186</v>
+        <v>0.1213</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.7145</v>
+        <v>0.1213</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0269</v>
+        <v>-0.9324</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5512</v>
+        <v>1.5055</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4757</v>
+        <v>-2.4379</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6851</v>
+        <v>-0.2427</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0276</v>
+        <v>0.4454</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.7128</v>
+        <v>-0.6881</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5313</v>
+        <v>1.7395</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1023</v>
+        <v>1.6181</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.1214</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1538</v>
+        <v>-1.9822</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0747</v>
+        <v>-1.1727</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0792</v>
+        <v>-0.8095</v>
       </c>
       <c r="P6" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>0.586</v>
+        <v>2.1488</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0722</v>
+        <v>0.3336</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0199</v>
+        <v>0.2236</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0921</v>
+        <v>0.11</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6114</v>
+        <v>-1.0269</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3141</v>
+        <v>-0.5512</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7027</v>
+        <v>-0.4757</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0879</v>
+        <v>-1.6851</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7107</v>
+        <v>0.0276</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3772</v>
+        <v>-1.7128</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.7887</v>
+        <v>-0.5313</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1423</v>
+        <v>0.1023</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6465</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2992</v>
+        <v>-1.1538</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5684</v>
+        <v>-0.0747</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2692</v>
+        <v>-1.0792</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7106</v>
+        <v>0.0722</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5415</v>
+        <v>-0.0199</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1691</v>
+        <v>0.0921</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4294</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.316</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8483</v>
+        <v>-1.6114</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0164</v>
+        <v>-2.3141</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.832</v>
+        <v>0.7027</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0769</v>
+        <v>-2.0879</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8475</v>
+        <v>-1.7107</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2294</v>
+        <v>-0.3772</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0814</v>
+        <v>-1.7887</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0409</v>
+        <v>-1.1423</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0405</v>
+        <v>-0.6465</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1583</v>
+        <v>-0.2992</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8885</v>
+        <v>-0.5684</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2698</v>
+        <v>0.2692</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7814</v>
+        <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2105</v>
+        <v>1.7106</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.121</v>
+        <v>0.5415</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.08939999999999999</v>
+        <v>1.1691</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3656</v>
+        <v>-1.4294</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3656</v>
+        <v>-2.316</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. HUGUET CARRASCO</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8856</v>
+        <v>-1.8483</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.145</v>
+        <v>-1.0164</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7407</v>
+        <v>-0.832</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0699</v>
+        <v>-1.0769</v>
       </c>
       <c r="H9" t="n">
-        <v>1.382</v>
+        <v>-0.8475</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6879</v>
+        <v>-0.2294</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6703</v>
+        <v>0.0814</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.0409</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6879</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3996</v>
+        <v>-1.1583</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3996</v>
+        <v>-0.8885</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.2698</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.7348</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0021</v>
+        <v>-0.2105</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1149</v>
+        <v>-0.121</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.117</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>-0.3656</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>-0.3656</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. HIDALGO GARRIGUES</t>
+          <t>L. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1784</v>
+        <v>-1.8856</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8425</v>
+        <v>-1.145</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3359</v>
+        <v>-0.7407</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7443</v>
+        <v>2.0699</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7391</v>
+        <v>1.382</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4834</v>
+        <v>0.6879</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9389</v>
+        <v>1.6703</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2648</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6741</v>
+        <v>0.6879</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1946</v>
+        <v>0.3996</v>
       </c>
       <c r="N10" t="n">
-        <v>1.0039</v>
+        <v>0.3996</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8093</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1953</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
         <v>0.1953</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1452</v>
+        <v>-0.0021</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1808</v>
+        <v>0.1149</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0357</v>
+        <v>-0.117</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4843</v>
+        <v>-1.2186</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7615</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>B. HIDALGO GARRIGUES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2973</v>
+        <v>-2.1784</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1872</v>
+        <v>-0.8425</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1101</v>
+        <v>-1.3359</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1059</v>
+        <v>-0.7443</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3382</v>
+        <v>0.7391</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4441</v>
+        <v>-1.4834</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6906</v>
+        <v>-0.9389</v>
       </c>
       <c r="K11" t="n">
-        <v>0.023</v>
+        <v>-0.2648</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7136</v>
+        <v>-0.6741</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5846</v>
+        <v>0.1946</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3152</v>
+        <v>1.0039</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2694</v>
+        <v>-0.8093</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.3441</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9258</v>
+        <v>-0.1452</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4335</v>
+        <v>-0.1808</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4923</v>
+        <v>0.0357</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7731</v>
+        <v>-1.4843</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7731</v>
+        <v>-1.7615</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>A. BENNASSAR ROSSELLO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4828</v>
+        <v>-3.9043</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7741</v>
+        <v>-3.7942</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2913</v>
+        <v>-0.1101</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.9349</v>
+        <v>-0.7129</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8585</v>
+        <v>0.3382</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0764</v>
+        <v>-1.0511</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4313</v>
+        <v>-1.2976</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1842</v>
+        <v>0.023</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.6155</v>
+        <v>-1.3206</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5036</v>
+        <v>0.5846</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0427</v>
+        <v>0.3152</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5391</v>
+        <v>0.2694</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.7581</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.9069</v>
+        <v>-2.9301</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0303</v>
+        <v>0.9258</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3454</v>
+        <v>0.4335</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6849</v>
+        <v>0.4923</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-1.7731</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.0388</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,1004 +1483,1393 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.638599999999999</v>
+        <v>-4.4828</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.058599999999999</v>
+        <v>-4.7741</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5803000000000003</v>
+        <v>0.2913</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3027000000000015</v>
+        <v>-2.9349</v>
       </c>
       <c r="H13" t="n">
-        <v>4.345299999999999</v>
+        <v>-0.8585</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.0426</v>
+        <v>-2.0764</v>
       </c>
       <c r="J13" t="n">
-        <v>5.9422</v>
+        <v>-2.4313</v>
       </c>
       <c r="K13" t="n">
-        <v>7.958399999999999</v>
+        <v>0.1842</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.0165</v>
+        <v>-2.6155</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.6395</v>
+        <v>-0.5036</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.6133</v>
+        <v>-1.0427</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.0263</v>
+        <v>0.5391</v>
       </c>
       <c r="P13" t="n">
-        <v>-8.7905</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q13" t="n">
-        <v>-23.4411</v>
+        <v>-3.9069</v>
       </c>
       <c r="R13" t="n">
-        <v>14.6507</v>
+        <v>2.1488</v>
       </c>
       <c r="S13" t="n">
-        <v>7.070599999999999</v>
+        <v>1.0303</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4774</v>
+        <v>0.3454</v>
       </c>
       <c r="U13" t="n">
-        <v>4.5934</v>
+        <v>0.6849</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.221399999999999</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>12.963</v>
+        <v>1.2186</v>
       </c>
       <c r="X13" t="n">
-        <v>-14.1848</v>
+        <v>-2.0388</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>CB ANDRATX</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.4932</v>
+        <v>-2.6386</v>
       </c>
       <c r="E14" t="n">
-        <v>6.2871</v>
+        <v>-2.0586</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2061</v>
+        <v>-0.5802999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8943</v>
+        <v>0.3027000000000011</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2648</v>
+        <v>4.345299999999998</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1591</v>
+        <v>-4.0426</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6684</v>
+        <v>5.9422</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0476</v>
+        <v>7.958399999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6208</v>
+        <v>-2.0165</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7741</v>
+        <v>-5.6395</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3123</v>
+        <v>-3.6133</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5383</v>
+        <v>-2.0263</v>
       </c>
       <c r="P14" t="n">
-        <v>3.3208</v>
+        <v>-8.7905</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1953</v>
+        <v>-23.4411</v>
       </c>
       <c r="R14" t="n">
-        <v>3.5162</v>
+        <v>14.6507</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2058</v>
+        <v>7.070599999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.947</v>
+        <v>2.4774</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2588</v>
+        <v>4.5934</v>
       </c>
       <c r="V14" t="n">
-        <v>5.4838</v>
+        <v>-1.2214</v>
       </c>
       <c r="W14" t="n">
-        <v>5.7611</v>
+        <v>12.963</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2772</v>
-      </c>
+        <v>-14.1848</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4137</v>
+        <v>5.7303</v>
       </c>
       <c r="E15" t="n">
-        <v>3.051</v>
+        <v>3.5242</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6373</v>
+        <v>2.2061</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3354</v>
+        <v>-1.8686</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0939</v>
+        <v>-3.0277</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4293</v>
+        <v>1.1591</v>
       </c>
       <c r="J15" t="n">
-        <v>2.299</v>
+        <v>-1.0945</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0041</v>
+        <v>-1.7153</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2949</v>
+        <v>0.6208</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9636</v>
+        <v>-0.7741</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.098</v>
+        <v>-1.3123</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1344</v>
+        <v>0.5383</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7581</v>
+        <v>3.3208</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>3.5162</v>
       </c>
       <c r="S15" t="n">
-        <v>0.203</v>
+        <v>-1.2058</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1975</v>
+        <v>-0.947</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0054</v>
+        <v>-0.2588</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.8828</v>
+        <v>5.4838</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5545</v>
+        <v>5.7611</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4373</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.857</v>
+        <v>2.7629</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5259</v>
+        <v>2.7629</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6689000000000001</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.09710000000000001</v>
+        <v>2.7629</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0156</v>
+        <v>2.7629</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0815</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0203</v>
+        <v>2.7629</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2919</v>
+        <v>2.7629</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7284</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1174</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3075</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8099</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5770999999999999</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0721</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5049</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>A. RECIO PIÑOL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7366</v>
+        <v>1.8279</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.5896</v>
+        <v>1.8279</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3262</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5202</v>
+        <v>1.8279</v>
       </c>
       <c r="H17" t="n">
-        <v>0.921</v>
+        <v>0.614</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.4412</v>
+        <v>1.214</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1277</v>
+        <v>1.8279</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0286</v>
+        <v>0.614</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9009</v>
+        <v>1.214</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.648</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1077</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5403</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.9069</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3879</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4552</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0673</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3244</v>
+        <v>0.7366</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4208</v>
+        <v>-1.5896</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7453</v>
+        <v>2.3262</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3829</v>
+        <v>-1.5202</v>
       </c>
       <c r="H18" t="n">
-        <v>0.437</v>
+        <v>0.921</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0541</v>
+        <v>-2.4412</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7972</v>
+        <v>0.1277</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7163</v>
+        <v>2.0286</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0809</v>
+        <v>-1.9009</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4144</v>
+        <v>-1.648</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2793</v>
+        <v>-1.1077</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.135</v>
+        <v>-0.5403</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-2.1488</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>3.9069</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2538</v>
+        <v>-0.3879</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2414</v>
+        <v>-0.4552</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0124</v>
+        <v>0.0673</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5255</v>
+        <v>0.607</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3417</v>
+        <v>0.607</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8162</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7675</v>
+        <v>0.607</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.304</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5365</v>
+        <v>0.607</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.468</v>
+        <v>0.607</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.1963</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7284</v>
+        <v>0.607</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2996</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1077</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8081</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.3208</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1487</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1622</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0136</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5679</v>
+        <v>0.3244</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4294</v>
+        <v>-0.4208</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1385</v>
+        <v>0.7453</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1257</v>
+        <v>0.3829</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1665</v>
+        <v>0.437</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0409</v>
+        <v>-0.0541</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3806</v>
+        <v>0.7972</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6127</v>
+        <v>0.7163</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7679</v>
+        <v>0.0809</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2549</v>
+        <v>-0.4144</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5538</v>
+        <v>-0.2793</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8087</v>
+        <v>-0.135</v>
       </c>
       <c r="P20" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9147999999999999</v>
+        <v>-0.2538</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5447</v>
+        <v>-0.2414</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3701</v>
+        <v>-0.0124</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6754</v>
+        <v>0.25</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.156</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5194</v>
+        <v>-0.6689000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>1.5655</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3625</v>
+        <v>-0.0156</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9279</v>
+        <v>-0.6885</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5205</v>
+        <v>1.4133</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2661</v>
+        <v>1.2919</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2544</v>
+        <v>0.1214</v>
       </c>
       <c r="M21" t="n">
-        <v>0.045</v>
+        <v>-2.1174</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-1.3075</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6735</v>
+        <v>-0.8099</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1255</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>2.9301</v>
+        <v>1.9534</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.159</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9883</v>
+        <v>-0.0721</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1707</v>
+        <v>-0.5049</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8865</v>
+        <v>0.5545</v>
       </c>
       <c r="W21" t="n">
-        <v>2.4373</v>
+        <v>0.5545</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.3238</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>A. RECIO PINOL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8298</v>
+        <v>-0.4143</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9514</v>
+        <v>1.2231</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1215</v>
+        <v>-1.6373</v>
       </c>
       <c r="G22" t="n">
-        <v>1.811</v>
+        <v>-0.4925</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5951</v>
+        <v>-0.7079</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2159</v>
+        <v>0.2154</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6863</v>
+        <v>0.471</v>
       </c>
       <c r="K22" t="n">
-        <v>1.7396</v>
+        <v>0.3901</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0533</v>
+        <v>0.0809</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1247</v>
+        <v>-0.9636</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1445</v>
+        <v>-1.098</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2692</v>
+        <v>0.1344</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3441</v>
+        <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3989</v>
+        <v>0.203</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7661</v>
+        <v>0.1975</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3672</v>
+        <v>0.0054</v>
       </c>
       <c r="V22" t="n">
+        <v>-1.8828</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X22" t="n">
         <v>-2.4373</v>
       </c>
-      <c r="W22" t="n">
-        <v>0.2772</v>
-      </c>
-      <c r="X22" t="n">
-        <v>-2.7145</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0286</v>
+        <v>-0.5255</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.155</v>
+        <v>-2.3417</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8736</v>
+        <v>1.8162</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8474</v>
+        <v>-1.7675</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.483</v>
+        <v>-3.304</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3644</v>
+        <v>1.5365</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9585</v>
+        <v>-1.468</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.999</v>
+        <v>-2.1963</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0405</v>
+        <v>0.7284</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8889</v>
+        <v>-0.2996</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.484</v>
+        <v>-1.1077</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4049</v>
+        <v>0.8081</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>-2.1488</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3674</v>
+        <v>3.3208</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5145</v>
+        <v>-1.1487</v>
       </c>
       <c r="T23" t="n">
-        <v>0.648</v>
+        <v>-1.1622</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1335</v>
+        <v>0.0136</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1097</v>
+        <v>1.2186</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1089</v>
+        <v>2.4373</v>
       </c>
       <c r="X23" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2107</v>
+        <v>-0.5679</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2399</v>
+        <v>-0.4294</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0292</v>
+        <v>-0.1385</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0663</v>
+        <v>-1.1257</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6078</v>
+        <v>-1.1665</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6741</v>
+        <v>0.0409</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6728</v>
+        <v>-1.3806</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6728</v>
+        <v>-0.6127</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-0.7679</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7391</v>
+        <v>0.2549</v>
       </c>
       <c r="N24" t="n">
-        <v>0.065</v>
+        <v>-0.5538</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6741</v>
+        <v>0.8087</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0.586</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3941</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.262</v>
+        <v>-0.5447</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1321</v>
+        <v>-0.3701</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.4921</v>
+        <v>0.8865</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.3283</v>
+        <v>1.4959</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.1638</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.987</v>
+        <v>-0.6754</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5802000000000009</v>
+        <v>-0.156</v>
       </c>
       <c r="F25" t="n">
+        <v>-0.5194</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.5655</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.3625</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.9279</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.5205</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.2661</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.2544</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.6284999999999999</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.6735</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-3.1255</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.9301</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-1.159</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.9883</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.1707</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.4373</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-3.3238</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>S. IBORRA BARRERA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.8298</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.9514</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.1215</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.811</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.5951</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2159</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.6863</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.7396</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.0533</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.1247</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.1445</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.3441</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.3989</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.7661</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-2.7145</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>G. HERETER MARCHANTE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-2.0286</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-1.155</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.8736</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-1.8474</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.483</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.3644</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.9585</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.999</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.8889</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.484</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.4049</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.5145</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.1335</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-0.1097</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.1089</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>M. SUAREZ CANOSA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-3.2107</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-3.2399</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.0292</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.6078</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.6741</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-0.6728</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.6728</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.7391</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.6741</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-0.3941</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.262</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.1321</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-2.4921</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-1.3283</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-1.1638</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484241_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3.9869</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.5802000000000027</v>
+      </c>
+      <c r="F29" t="n">
         <v>3.4068</v>
       </c>
-      <c r="G25" t="n">
-        <v>-0.3025000000000002</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="G29" t="n">
+        <v>-0.3024999999999998</v>
+      </c>
+      <c r="H29" t="n">
         <v>-4.345</v>
       </c>
-      <c r="I25" t="n">
-        <v>4.0425</v>
-      </c>
-      <c r="J25" t="n">
-        <v>5.639500000000001</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.613400000000001</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="I29" t="n">
+        <v>4.0426</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5.6394</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.6134</v>
+      </c>
+      <c r="L29" t="n">
         <v>2.0262</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M29" t="n">
         <v>-5.9423</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N29" t="n">
         <v>-7.958299999999999</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O29" t="n">
         <v>2.0162</v>
       </c>
-      <c r="P25" t="n">
-        <v>8.790399999999998</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="P29" t="n">
+        <v>8.7904</v>
+      </c>
+      <c r="Q29" t="n">
         <v>-14.6507</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R29" t="n">
         <v>23.4411</v>
       </c>
-      <c r="S25" t="n">
-        <v>-5.722600000000001</v>
-      </c>
-      <c r="T25" t="n">
-        <v>-4.593500000000001</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="S29" t="n">
+        <v>-5.7226</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-4.593499999999999</v>
+      </c>
+      <c r="U29" t="n">
         <v>-1.129</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V29" t="n">
         <v>1.2215</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W29" t="n">
         <v>14.1849</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X29" t="n">
         <v>-12.9631</v>
       </c>
+      <c r="Y29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
